--- a/artifacts/aura-forecast/public/exports/Model_Performance_Report.xlsx
+++ b/artifacts/aura-forecast/public/exports/Model_Performance_Report.xlsx
@@ -3,6 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Model_Performance" sheetId="1" r:id="rId1"/>
+    <sheet name="Analysis_Charts" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -178,4 +179,215 @@
     </row>
   </sheetData>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Analysis item</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>MAE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>26.136164</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RMSE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>31.693458</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>R²</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>-4.695695</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Bias</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>-23.726993</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MAPE</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7.119203</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Visual asset</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>analytics/data_quality_missingness.svg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Missing percentage by variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>analytics/data_quality_outliers.svg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Flagged outlier counts by variable</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>analytics/hist_temperature.svg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Temperature histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>analytics/hist_pressure.svg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Pressure histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>analytics/hist_refractivity.svg</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Refractivity histogram</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>analytics/correlation_refractivity.svg</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Predictor correlation with refractivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>analytics/daily_refractivity.svg</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Daily refractivity trend</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>analytics/monthly_forecast.svg</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Monthly forecast comparison</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>analytics/validation_metrics.svg</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Chronological validation scorecard</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>analytics/training_holdout_rows.svg</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Training, holdout, and validation counts</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/artifacts/aura-forecast/public/exports/Model_Performance_Report.xlsx
+++ b/artifacts/aura-forecast/public/exports/Model_Performance_Report.xlsx
@@ -113,7 +113,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26.136164</t>
+          <t>3.193933</t>
         </is>
       </c>
     </row>
@@ -125,7 +125,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31.693458</t>
+          <t>3.972661</t>
         </is>
       </c>
     </row>
@@ -137,7 +137,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-4.695695</t>
+          <t>0.910511</t>
         </is>
       </c>
     </row>
@@ -149,7 +149,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-23.726993</t>
+          <t>1.037282</t>
         </is>
       </c>
     </row>
@@ -161,7 +161,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7.119203</t>
+          <t>0.883242</t>
         </is>
       </c>
     </row>
@@ -204,7 +204,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26.136164</t>
+          <t>3.193933</t>
         </is>
       </c>
     </row>
@@ -216,7 +216,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31.693458</t>
+          <t>3.972661</t>
         </is>
       </c>
     </row>
@@ -228,7 +228,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-4.695695</t>
+          <t>0.910511</t>
         </is>
       </c>
     </row>
@@ -240,7 +240,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-23.726993</t>
+          <t>1.037282</t>
         </is>
       </c>
     </row>
@@ -252,7 +252,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.119203</t>
+          <t>0.883242</t>
         </is>
       </c>
     </row>
